--- a/docs/data-templates/samples/分析主体及汇总映射.xlsx
+++ b/docs/data-templates/samples/分析主体及汇总映射.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr codeName="ThisWorkbook"/>
   <bookViews>
-    <workbookView windowWidth="20280" windowHeight="11325" activeTab="3"/>
+    <workbookView windowWidth="31229" windowHeight="14212" activeTab="6"/>
   </bookViews>
   <sheets>
     <sheet name="单体主体" sheetId="6" r:id="rId1"/>
@@ -847,7 +847,7 @@
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="24">
+  <fonts count="23">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -864,13 +864,6 @@
       <sz val="10"/>
       <name val="微软雅黑"/>
       <charset val="134"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
     </font>
     <font>
       <u/>
@@ -1357,13 +1350,16 @@
     <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -1372,121 +1368,118 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="3" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="3" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="4" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="4" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="5" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="5" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
@@ -1507,7 +1500,7 @@
     <xf numFmtId="49" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" readingOrder="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -1816,8 +1809,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="13603605" y="838200"/>
-          <a:ext cx="3571875" cy="1971675"/>
+          <a:off x="12809855" y="825500"/>
+          <a:ext cx="3375025" cy="1943100"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -2123,7 +2116,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr codeName="Sheet1"/>
   <dimension ref="A1:B11"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="1"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="15" outlineLevelCol="1"/>
   <sheetData>
     <row r="1" spans="1:2">
       <c r="A1" s="6" t="s">
@@ -2223,7 +2216,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr codeName="Sheet2"/>
   <dimension ref="A1:B11"/>
-  <sheetFormatPr defaultColWidth="8.88333333333333" defaultRowHeight="13.5" outlineLevelCol="1"/>
+  <sheetFormatPr defaultColWidth="8.88495575221239" defaultRowHeight="15" outlineLevelCol="1"/>
   <sheetData>
     <row r="1" spans="1:2">
       <c r="A1" s="6" t="s">
@@ -2323,7 +2316,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr codeName="Sheet3"/>
   <dimension ref="A1"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="15"/>
   <sheetData/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter/>
@@ -2334,9 +2327,9 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr codeName="Sheet14"/>
   <dimension ref="A1:B11"/>
-  <sheetFormatPr defaultColWidth="8.88333333333333" defaultRowHeight="13.5" outlineLevelCol="1"/>
+  <sheetFormatPr defaultColWidth="8.88495575221239" defaultRowHeight="15" outlineLevelCol="1"/>
   <cols>
-    <col min="1" max="1" width="49.4416666666667" customWidth="1"/>
+    <col min="1" max="1" width="49.4424778761062" customWidth="1"/>
     <col min="2" max="2" width="75" customWidth="1"/>
   </cols>
   <sheetData>
@@ -2438,7 +2431,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr codeName="Sheet35"/>
   <dimension ref="A1:E6"/>
-  <sheetFormatPr defaultColWidth="8.88333333333333" defaultRowHeight="13.5" outlineLevelRow="5" outlineLevelCol="4"/>
+  <sheetFormatPr defaultColWidth="8.88495575221239" defaultRowHeight="15" outlineLevelRow="5" outlineLevelCol="4"/>
   <cols>
     <col min="1" max="1" width="16" customWidth="1"/>
   </cols>
@@ -2531,14 +2524,14 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr codeName="Sheet4"/>
   <dimension ref="B1:F117"/>
-  <sheetFormatPr defaultColWidth="8.88333333333333" defaultRowHeight="16.5" outlineLevelCol="5"/>
+  <sheetFormatPr defaultColWidth="8.88495575221239" defaultRowHeight="16.25" outlineLevelCol="5"/>
   <cols>
-    <col min="1" max="1" width="8.88333333333333" style="1"/>
-    <col min="2" max="2" width="16.1083333333333" style="1" customWidth="1"/>
-    <col min="3" max="3" width="42.3333333333333" style="1" customWidth="1"/>
-    <col min="4" max="5" width="37.2166666666667" style="1" customWidth="1"/>
-    <col min="6" max="6" width="27.8833333333333" style="1" customWidth="1"/>
-    <col min="7" max="16384" width="8.88333333333333" style="1"/>
+    <col min="1" max="1" width="8.88495575221239" style="1"/>
+    <col min="2" max="2" width="16.1061946902655" style="1" customWidth="1"/>
+    <col min="3" max="3" width="42.3362831858407" style="1" customWidth="1"/>
+    <col min="4" max="5" width="37.212389380531" style="1" customWidth="1"/>
+    <col min="6" max="6" width="27.8849557522124" style="1" customWidth="1"/>
+    <col min="7" max="16384" width="8.88495575221239" style="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="2:6">
@@ -4356,11 +4349,11 @@
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr filterMode="1" codeName="Sheet6"/>
+  <sheetPr codeName="Sheet6"/>
   <dimension ref="A1:C153"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="2"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="15" outlineLevelCol="2"/>
   <cols>
-    <col min="1" max="1" width="37.8833333333333" customWidth="1"/>
+    <col min="1" max="1" width="37.8849557522124" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
@@ -4429,7 +4422,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="7" hidden="1" spans="1:3">
+    <row r="7" spans="1:3">
       <c r="A7" t="s">
         <v>178</v>
       </c>
@@ -4440,7 +4433,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="8" hidden="1" spans="1:3">
+    <row r="8" spans="1:3">
       <c r="A8" t="s">
         <v>183</v>
       </c>
@@ -4451,7 +4444,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="9" hidden="1" spans="1:3">
+    <row r="9" spans="1:3">
       <c r="A9" t="s">
         <v>213</v>
       </c>
@@ -4517,7 +4510,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="15" hidden="1" spans="1:3">
+    <row r="15" spans="1:3">
       <c r="A15" t="s">
         <v>179</v>
       </c>
@@ -4528,7 +4521,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="16" hidden="1" spans="1:3">
+    <row r="16" spans="1:3">
       <c r="A16" t="s">
         <v>180</v>
       </c>
@@ -4539,7 +4532,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="17" hidden="1" spans="1:3">
+    <row r="17" spans="1:3">
       <c r="A17" t="s">
         <v>181</v>
       </c>
@@ -4638,7 +4631,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="26" hidden="1" spans="1:3">
+    <row r="26" spans="1:3">
       <c r="A26" t="s">
         <v>74</v>
       </c>
@@ -4649,7 +4642,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="27" hidden="1" spans="1:3">
+    <row r="27" spans="1:3">
       <c r="A27" t="s">
         <v>75</v>
       </c>
@@ -4671,7 +4664,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="29" hidden="1" spans="1:3">
+    <row r="29" spans="1:3">
       <c r="A29" t="s">
         <v>97</v>
       </c>
@@ -4693,7 +4686,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="31" hidden="1" spans="1:3">
+    <row r="31" spans="1:3">
       <c r="A31" t="s">
         <v>101</v>
       </c>
@@ -4715,7 +4708,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="33" hidden="1" spans="1:3">
+    <row r="33" spans="1:3">
       <c r="A33" t="s">
         <v>123</v>
       </c>
@@ -4737,7 +4730,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="35" hidden="1" spans="1:3">
+    <row r="35" spans="1:3">
       <c r="A35" t="s">
         <v>127</v>
       </c>
@@ -4781,12 +4774,12 @@
         <v>69</v>
       </c>
     </row>
-    <row r="39" hidden="1" spans="1:3">
+    <row r="39" spans="1:3">
       <c r="A39" t="s">
         <v>153</v>
       </c>
       <c r="B39" t="s">
-        <v>229</v>
+        <v>227</v>
       </c>
       <c r="C39" t="s">
         <v>69</v>
@@ -4803,7 +4796,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="41" hidden="1" spans="1:3">
+    <row r="41" spans="1:3">
       <c r="A41" t="s">
         <v>177</v>
       </c>
@@ -4858,7 +4851,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="46" hidden="1" spans="1:3">
+    <row r="46" spans="1:3">
       <c r="A46" t="s">
         <v>216</v>
       </c>
@@ -4869,7 +4862,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="47" hidden="1" spans="1:3">
+    <row r="47" spans="1:3">
       <c r="A47" t="s">
         <v>217</v>
       </c>
@@ -4880,7 +4873,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="48" hidden="1" spans="1:3">
+    <row r="48" spans="1:3">
       <c r="A48" t="s">
         <v>219</v>
       </c>
@@ -4891,7 +4884,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="49" hidden="1" spans="1:3">
+    <row r="49" spans="1:3">
       <c r="A49" t="s">
         <v>220</v>
       </c>
@@ -4902,7 +4895,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="50" hidden="1" spans="1:3">
+    <row r="50" spans="1:3">
       <c r="A50" t="s">
         <v>222</v>
       </c>
@@ -4913,7 +4906,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="51" hidden="1" spans="1:3">
+    <row r="51" spans="1:3">
       <c r="A51" t="s">
         <v>223</v>
       </c>
@@ -4946,7 +4939,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="54" hidden="1" spans="1:3">
+    <row r="54" spans="1:3">
       <c r="A54" t="s">
         <v>91</v>
       </c>
@@ -4957,7 +4950,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="55" hidden="1" spans="1:3">
+    <row r="55" spans="1:3">
       <c r="A55" t="s">
         <v>92</v>
       </c>
@@ -4968,7 +4961,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="56" hidden="1" spans="1:3">
+    <row r="56" spans="1:3">
       <c r="A56" t="s">
         <v>93</v>
       </c>
@@ -4979,7 +4972,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="57" hidden="1" spans="1:3">
+    <row r="57" spans="1:3">
       <c r="A57" t="s">
         <v>94</v>
       </c>
@@ -4990,7 +4983,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="58" hidden="1" spans="1:3">
+    <row r="58" spans="1:3">
       <c r="A58" t="s">
         <v>95</v>
       </c>
@@ -5001,7 +4994,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="59" hidden="1" spans="1:3">
+    <row r="59" spans="1:3">
       <c r="A59" t="s">
         <v>96</v>
       </c>
@@ -5012,7 +5005,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="60" hidden="1" spans="1:3">
+    <row r="60" spans="1:3">
       <c r="A60" t="s">
         <v>99</v>
       </c>
@@ -5023,7 +5016,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="61" hidden="1" spans="1:3">
+    <row r="61" spans="1:3">
       <c r="A61" t="s">
         <v>100</v>
       </c>
@@ -5056,7 +5049,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="64" hidden="1" spans="1:3">
+    <row r="64" spans="1:3">
       <c r="A64" t="s">
         <v>117</v>
       </c>
@@ -5067,7 +5060,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="65" hidden="1" spans="1:3">
+    <row r="65" spans="1:3">
       <c r="A65" t="s">
         <v>118</v>
       </c>
@@ -5078,7 +5071,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="66" hidden="1" spans="1:3">
+    <row r="66" spans="1:3">
       <c r="A66" t="s">
         <v>119</v>
       </c>
@@ -5089,7 +5082,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="67" hidden="1" spans="1:3">
+    <row r="67" spans="1:3">
       <c r="A67" t="s">
         <v>120</v>
       </c>
@@ -5100,7 +5093,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="68" hidden="1" spans="1:3">
+    <row r="68" spans="1:3">
       <c r="A68" t="s">
         <v>121</v>
       </c>
@@ -5111,7 +5104,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="69" hidden="1" spans="1:3">
+    <row r="69" spans="1:3">
       <c r="A69" t="s">
         <v>122</v>
       </c>
@@ -5122,7 +5115,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="70" hidden="1" spans="1:3">
+    <row r="70" spans="1:3">
       <c r="A70" t="s">
         <v>125</v>
       </c>
@@ -5133,7 +5126,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="71" hidden="1" spans="1:3">
+    <row r="71" spans="1:3">
       <c r="A71" t="s">
         <v>126</v>
       </c>
@@ -5166,89 +5159,89 @@
         <v>70</v>
       </c>
     </row>
-    <row r="74" hidden="1" spans="1:3">
+    <row r="74" spans="1:3">
       <c r="A74" t="s">
         <v>143</v>
       </c>
       <c r="B74" t="s">
-        <v>229</v>
+        <v>227</v>
       </c>
       <c r="C74" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="75" hidden="1" spans="1:3">
+    <row r="75" spans="1:3">
       <c r="A75" t="s">
         <v>144</v>
       </c>
       <c r="B75" t="s">
-        <v>229</v>
+        <v>227</v>
       </c>
       <c r="C75" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="76" hidden="1" spans="1:3">
+    <row r="76" spans="1:3">
       <c r="A76" t="s">
         <v>145</v>
       </c>
       <c r="B76" t="s">
-        <v>229</v>
+        <v>227</v>
       </c>
       <c r="C76" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="77" hidden="1" spans="1:3">
+    <row r="77" spans="1:3">
       <c r="A77" t="s">
         <v>146</v>
       </c>
       <c r="B77" t="s">
-        <v>229</v>
+        <v>227</v>
       </c>
       <c r="C77" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="78" hidden="1" spans="1:3">
+    <row r="78" spans="1:3">
       <c r="A78" t="s">
         <v>147</v>
       </c>
       <c r="B78" t="s">
-        <v>229</v>
+        <v>227</v>
       </c>
       <c r="C78" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="79" hidden="1" spans="1:3">
+    <row r="79" spans="1:3">
       <c r="A79" t="s">
         <v>148</v>
       </c>
       <c r="B79" t="s">
-        <v>229</v>
+        <v>227</v>
       </c>
       <c r="C79" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" hidden="1" spans="1:3">
+    <row r="80" spans="1:3">
       <c r="A80" t="s">
         <v>151</v>
       </c>
       <c r="B80" t="s">
-        <v>229</v>
+        <v>227</v>
       </c>
       <c r="C80" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="81" hidden="1" spans="1:3">
+    <row r="81" spans="1:3">
       <c r="A81" t="s">
         <v>152</v>
       </c>
       <c r="B81" t="s">
-        <v>229</v>
+        <v>227</v>
       </c>
       <c r="C81" t="s">
         <v>70</v>
@@ -5276,7 +5269,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="84" hidden="1" spans="1:3">
+    <row r="84" spans="1:3">
       <c r="A84" t="s">
         <v>182</v>
       </c>
@@ -5397,7 +5390,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="95" hidden="1" spans="1:3">
+    <row r="95" spans="1:3">
       <c r="A95" t="s">
         <v>80</v>
       </c>
@@ -5408,7 +5401,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="96" hidden="1" spans="1:3">
+    <row r="96" spans="1:3">
       <c r="A96" t="s">
         <v>81</v>
       </c>
@@ -5419,7 +5412,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="97" hidden="1" spans="1:3">
+    <row r="97" spans="1:3">
       <c r="A97" t="s">
         <v>82</v>
       </c>
@@ -5430,7 +5423,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="98" hidden="1" spans="1:3">
+    <row r="98" spans="1:3">
       <c r="A98" t="s">
         <v>83</v>
       </c>
@@ -5441,7 +5434,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="99" hidden="1" spans="1:3">
+    <row r="99" spans="1:3">
       <c r="A99" t="s">
         <v>84</v>
       </c>
@@ -5452,7 +5445,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="100" hidden="1" spans="1:3">
+    <row r="100" spans="1:3">
       <c r="A100" t="s">
         <v>85</v>
       </c>
@@ -5463,7 +5456,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="101" hidden="1" spans="1:3">
+    <row r="101" spans="1:3">
       <c r="A101" t="s">
         <v>86</v>
       </c>
@@ -5474,7 +5467,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="102" hidden="1" spans="1:3">
+    <row r="102" spans="1:3">
       <c r="A102" t="s">
         <v>88</v>
       </c>
@@ -5485,7 +5478,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="103" hidden="1" spans="1:3">
+    <row r="103" spans="1:3">
       <c r="A103" t="s">
         <v>89</v>
       </c>
@@ -5496,7 +5489,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="104" hidden="1" spans="1:3">
+    <row r="104" spans="1:3">
       <c r="A104" t="s">
         <v>90</v>
       </c>
@@ -5507,7 +5500,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="105" hidden="1" spans="1:3">
+    <row r="105" spans="1:3">
       <c r="A105" t="s">
         <v>106</v>
       </c>
@@ -5518,7 +5511,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="106" hidden="1" spans="1:3">
+    <row r="106" spans="1:3">
       <c r="A106" t="s">
         <v>107</v>
       </c>
@@ -5529,7 +5522,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="107" hidden="1" spans="1:3">
+    <row r="107" spans="1:3">
       <c r="A107" t="s">
         <v>108</v>
       </c>
@@ -5540,7 +5533,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="108" hidden="1" spans="1:3">
+    <row r="108" spans="1:3">
       <c r="A108" t="s">
         <v>109</v>
       </c>
@@ -5551,7 +5544,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="109" hidden="1" spans="1:3">
+    <row r="109" spans="1:3">
       <c r="A109" t="s">
         <v>110</v>
       </c>
@@ -5562,7 +5555,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="110" hidden="1" spans="1:3">
+    <row r="110" spans="1:3">
       <c r="A110" t="s">
         <v>111</v>
       </c>
@@ -5573,7 +5566,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="111" hidden="1" spans="1:3">
+    <row r="111" spans="1:3">
       <c r="A111" t="s">
         <v>112</v>
       </c>
@@ -5584,7 +5577,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="112" hidden="1" spans="1:3">
+    <row r="112" spans="1:3">
       <c r="A112" t="s">
         <v>114</v>
       </c>
@@ -5595,7 +5588,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="113" hidden="1" spans="1:3">
+    <row r="113" spans="1:3">
       <c r="A113" t="s">
         <v>115</v>
       </c>
@@ -5606,7 +5599,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="114" hidden="1" spans="1:3">
+    <row r="114" spans="1:3">
       <c r="A114" t="s">
         <v>116</v>
       </c>
@@ -5727,7 +5720,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="125" hidden="1" spans="1:3">
+    <row r="125" spans="1:3">
       <c r="A125" t="s">
         <v>158</v>
       </c>
@@ -5738,7 +5731,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="126" hidden="1" spans="1:3">
+    <row r="126" spans="1:3">
       <c r="A126" t="s">
         <v>159</v>
       </c>
@@ -5749,7 +5742,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="127" hidden="1" spans="1:3">
+    <row r="127" spans="1:3">
       <c r="A127" t="s">
         <v>160</v>
       </c>
@@ -5760,7 +5753,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="128" hidden="1" spans="1:3">
+    <row r="128" spans="1:3">
       <c r="A128" t="s">
         <v>161</v>
       </c>
@@ -5771,7 +5764,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="129" hidden="1" spans="1:3">
+    <row r="129" spans="1:3">
       <c r="A129" t="s">
         <v>162</v>
       </c>
@@ -5782,7 +5775,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="130" hidden="1" spans="1:3">
+    <row r="130" spans="1:3">
       <c r="A130" t="s">
         <v>163</v>
       </c>
@@ -5793,7 +5786,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="131" hidden="1" spans="1:3">
+    <row r="131" spans="1:3">
       <c r="A131" t="s">
         <v>164</v>
       </c>
@@ -5804,7 +5797,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="132" hidden="1" spans="1:3">
+    <row r="132" spans="1:3">
       <c r="A132" t="s">
         <v>165</v>
       </c>
@@ -5815,7 +5808,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="133" hidden="1" spans="1:3">
+    <row r="133" spans="1:3">
       <c r="A133" t="s">
         <v>166</v>
       </c>
@@ -5826,7 +5819,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="134" hidden="1" spans="1:3">
+    <row r="134" spans="1:3">
       <c r="A134" t="s">
         <v>167</v>
       </c>
@@ -5837,7 +5830,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="135" hidden="1" spans="1:3">
+    <row r="135" spans="1:3">
       <c r="A135" t="s">
         <v>168</v>
       </c>
@@ -5848,7 +5841,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="136" hidden="1" spans="1:3">
+    <row r="136" spans="1:3">
       <c r="A136" t="s">
         <v>169</v>
       </c>
@@ -5859,7 +5852,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="137" hidden="1" spans="1:3">
+    <row r="137" spans="1:3">
       <c r="A137" t="s">
         <v>170</v>
       </c>
@@ -5870,7 +5863,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="138" hidden="1" spans="1:3">
+    <row r="138" spans="1:3">
       <c r="A138" t="s">
         <v>171</v>
       </c>
@@ -5881,7 +5874,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="139" hidden="1" spans="1:3">
+    <row r="139" spans="1:3">
       <c r="A139" t="s">
         <v>172</v>
       </c>
@@ -5892,7 +5885,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="140" hidden="1" spans="1:3">
+    <row r="140" spans="1:3">
       <c r="A140" t="s">
         <v>173</v>
       </c>
@@ -5903,7 +5896,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="141" hidden="1" spans="1:3">
+    <row r="141" spans="1:3">
       <c r="A141" t="s">
         <v>174</v>
       </c>
@@ -5914,7 +5907,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="142" hidden="1" spans="1:3">
+    <row r="142" spans="1:3">
       <c r="A142" t="s">
         <v>176</v>
       </c>
@@ -6048,11 +6041,6 @@
     </row>
   </sheetData>
   <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A1:C153" etc:filterBottomFollowUsedRange="0">
-    <filterColumn colId="1">
-      <customFilters>
-        <customFilter operator="equal" val="计算类"/>
-      </customFilters>
-    </filterColumn>
     <extLst/>
   </autoFilter>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -6065,7 +6053,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr codeName="Sheet5"/>
   <dimension ref="A1:B33"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="1"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="15" outlineLevelCol="1"/>
   <sheetData>
     <row r="1" spans="1:2">
       <c r="A1" t="s">
@@ -6293,9 +6281,9 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr codeName="Sheet7"/>
   <dimension ref="A1:C35"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="2"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="15" outlineLevelCol="2"/>
   <cols>
-    <col min="1" max="1" width="31.6666666666667" customWidth="1"/>
+    <col min="1" max="1" width="31.6637168141593" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
